--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\웹케시\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B8510D-6CCE-479E-AB5D-A002F1D04526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F11995-F894-4C90-B36A-A0CB89E68DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZAWUEBbwhB8zeQ4Q9DEnb/rF6VPyout8c4jSfiXtzDtdU7qqn/OoxNOy+/YKBXP/YEhLETtg/vLs6GA69T0smg==" workbookSaltValue="J5IV6q6u/Sx2UtLaGRQZQw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-13005" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
   <si>
     <t>상품명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -218,14 +218,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>신세계 이마트 100,000원 상품권 교환권</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>신세계 이마트 50,000원 상품권 교환권</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>신세계 이마트100,000원 상품권 교환권</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -252,26 +244,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>경리나라_파워블로거_4월</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>01052450621</t>
-  </si>
-  <si>
-    <t>01095052465</t>
-  </si>
-  <si>
-    <t>01058000072</t>
-  </si>
-  <si>
-    <t>01087765264</t>
-  </si>
-  <si>
-    <t>01048264600</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>윤소진 / 주임</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -285,6 +257,10 @@
   </si>
   <si>
     <t>02-3774-2781</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경리나라_파워블로거_N월</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1017,28 +993,112 @@
     <xf numFmtId="49" fontId="16" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
@@ -1047,6 +1107,110 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="justify" wrapText="1"/>
       <protection hidden="1"/>
@@ -1083,15 +1247,6 @@
       <alignment horizontal="left" vertical="justify" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1104,29 +1259,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1135,170 +1275,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1733,150 +1709,150 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
     </row>
     <row r="2" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
+      <c r="A2" s="39"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
     </row>
     <row r="3" spans="1:13" ht="14.1" customHeight="1" thickBot="1">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="97"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
     </row>
     <row r="4" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="87"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="43"/>
     </row>
     <row r="5" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="33" t="s">
+      <c r="B5" s="52"/>
+      <c r="C5" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="35"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="92"/>
+      <c r="L5" s="93"/>
     </row>
     <row r="6" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="58" t="s">
+      <c r="B6" s="52"/>
+      <c r="C6" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="50" t="s">
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="37"/>
-      <c r="I6" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="57"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="73"/>
     </row>
     <row r="7" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="50" t="s">
+      <c r="B7" s="52"/>
+      <c r="C7" s="67" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="37"/>
-      <c r="I7" s="110" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="57"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="106" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="73"/>
     </row>
     <row r="8" spans="1:13" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="51" t="s">
+      <c r="B8" s="48"/>
+      <c r="C8" s="103" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="52"/>
-      <c r="I8" s="53" t="s">
-        <v>57</v>
-      </c>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="55"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="103" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="104"/>
+      <c r="K8" s="104"/>
+      <c r="L8" s="105"/>
     </row>
     <row r="9" spans="1:13" ht="9.9499999999999993" customHeight="1" thickBot="1">
       <c r="A9" s="5"/>
@@ -1893,121 +1869,121 @@
       <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
-      <c r="J10" s="86"/>
-      <c r="K10" s="86"/>
-      <c r="L10" s="87"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="43"/>
     </row>
     <row r="11" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="98" t="s">
+      <c r="B11" s="52"/>
+      <c r="C11" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="100"/>
-      <c r="G11" s="108" t="s">
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="109"/>
-      <c r="I11" s="106">
+      <c r="H11" s="60"/>
+      <c r="I11" s="56">
         <v>46111</v>
       </c>
-      <c r="J11" s="99"/>
-      <c r="K11" s="99"/>
-      <c r="L11" s="107"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="57"/>
     </row>
     <row r="12" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="56"/>
-      <c r="L12" s="57"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="68"/>
+      <c r="L12" s="73"/>
     </row>
     <row r="13" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A13" s="101" t="str">
+      <c r="A13" s="49" t="str">
         <f>"문자 제목"&amp;" (현재 "&amp;LENB(C13)&amp;"byte)"</f>
         <v>문자 제목 (현재 33byte)</v>
       </c>
-      <c r="B13" s="102"/>
-      <c r="C13" s="93" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="95"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="72"/>
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="81" customHeight="1">
-      <c r="A14" s="101" t="str">
+      <c r="A14" s="49" t="str">
         <f>"문자 내용"&amp;" (현재 "&amp;LENB(C14)&amp;"byte)"</f>
         <v>문자 내용 (현재 342byte)</v>
       </c>
-      <c r="B14" s="102"/>
-      <c r="C14" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="70"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="78"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="79"/>
     </row>
     <row r="15" spans="1:13" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="65" t="s">
+      <c r="B15" s="48"/>
+      <c r="C15" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="51" t="s">
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="52"/>
-      <c r="I15" s="103" t="s">
+      <c r="H15" s="48"/>
+      <c r="I15" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="104"/>
-      <c r="K15" s="104"/>
-      <c r="L15" s="105"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="55"/>
     </row>
     <row r="16" spans="1:13" ht="9.9499999999999993" customHeight="1" thickBot="1">
       <c r="A16" s="5"/>
@@ -2024,31 +2000,31 @@
       <c r="L16" s="8"/>
     </row>
     <row r="17" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A17" s="85" t="s">
+      <c r="A17" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="86"/>
-      <c r="G17" s="86"/>
-      <c r="H17" s="86"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="87"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="43"/>
     </row>
     <row r="18" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="91" t="s">
+      <c r="B18" s="52"/>
+      <c r="C18" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="91"/>
-      <c r="E18" s="91"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
       <c r="F18" s="9" t="s">
         <v>9</v>
       </c>
@@ -2064,21 +2040,21 @@
       <c r="J18" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K18" s="50" t="s">
+      <c r="K18" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="L18" s="84"/>
+      <c r="L18" s="62"/>
     </row>
     <row r="19" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A19" s="92" t="s">
+      <c r="A19" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="90"/>
-      <c r="C19" s="88" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="89"/>
-      <c r="E19" s="90"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="36"/>
+      <c r="E19" s="34"/>
       <c r="F19" s="10">
         <v>100000</v>
       </c>
@@ -2090,25 +2066,25 @@
         <v>98000</v>
       </c>
       <c r="I19" s="12">
-        <v>5</v>
-      </c>
-      <c r="J19" s="30">
+        <v>0</v>
+      </c>
+      <c r="J19" s="30" t="str">
         <f t="shared" ref="J19" si="1">IFERROR(IF(H19*I19=0,"",H19*I19),"")</f>
-        <v>490000</v>
-      </c>
-      <c r="K19" s="38"/>
-      <c r="L19" s="83"/>
+        <v/>
+      </c>
+      <c r="K19" s="37"/>
+      <c r="L19" s="38"/>
     </row>
     <row r="20" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A20" s="92" t="s">
+      <c r="A20" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="88" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="89"/>
-      <c r="E20" s="90"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="36"/>
+      <c r="E20" s="34"/>
       <c r="F20" s="10">
         <v>50000</v>
       </c>
@@ -2120,21 +2096,21 @@
         <v>49000</v>
       </c>
       <c r="I20" s="12">
-        <v>1</v>
-      </c>
-      <c r="J20" s="30">
+        <v>0</v>
+      </c>
+      <c r="J20" s="30" t="str">
         <f t="shared" ref="J20" si="2">IFERROR(IF(H20*I20=0,"",H20*I20),"")</f>
-        <v>49000</v>
-      </c>
-      <c r="K20" s="38"/>
-      <c r="L20" s="83"/>
+        <v/>
+      </c>
+      <c r="K20" s="37"/>
+      <c r="L20" s="38"/>
     </row>
     <row r="21" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A21" s="71"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="40"/>
+      <c r="A21" s="66"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="64"/>
       <c r="F21" s="10"/>
       <c r="G21" s="14"/>
       <c r="H21" s="11" t="str">
@@ -2146,15 +2122,15 @@
         <f t="shared" ref="J21:J24" si="4">IFERROR(IF(H21*I21=0,"",H21*I21),"")</f>
         <v/>
       </c>
-      <c r="K21" s="38"/>
-      <c r="L21" s="83"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="38"/>
     </row>
     <row r="22" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A22" s="71"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="40"/>
+      <c r="A22" s="66"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="64"/>
       <c r="F22" s="10"/>
       <c r="G22" s="14"/>
       <c r="H22" s="11" t="str">
@@ -2166,15 +2142,15 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K22" s="38"/>
-      <c r="L22" s="83"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="38"/>
     </row>
     <row r="23" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A23" s="71"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="40"/>
+      <c r="A23" s="66"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="64"/>
       <c r="F23" s="15"/>
       <c r="G23" s="14"/>
       <c r="H23" s="11" t="str">
@@ -2186,15 +2162,15 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K23" s="38"/>
-      <c r="L23" s="83"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="38"/>
     </row>
     <row r="24" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A24" s="71"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="40"/>
+      <c r="A24" s="66"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="64"/>
       <c r="F24" s="15"/>
       <c r="G24" s="14"/>
       <c r="H24" s="11" t="str">
@@ -2206,30 +2182,30 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K24" s="38"/>
-      <c r="L24" s="83"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="38"/>
     </row>
     <row r="25" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A25" s="78" t="s">
+      <c r="A25" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="17">
+      <c r="B25" s="87"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="H25" s="88"/>
+      <c r="I25" s="17" t="str">
         <f>IFERROR(IF(SUM(I19:I24)=0,"",SUM(I19:I24)),"")</f>
-        <v>6</v>
-      </c>
-      <c r="J25" s="18">
+        <v/>
+      </c>
+      <c r="J25" s="18" t="str">
         <f>IFERROR(IF(SUM(J19:J24)=0,"",SUM(J19:J24)),"")</f>
-        <v>539000</v>
-      </c>
-      <c r="K25" s="81"/>
-      <c r="L25" s="82"/>
+        <v/>
+      </c>
+      <c r="K25" s="89"/>
+      <c r="L25" s="90"/>
     </row>
     <row r="26" spans="1:12" ht="9.9499999999999993" customHeight="1" thickBot="1">
       <c r="A26" s="8"/>
@@ -2246,49 +2222,49 @@
       <c r="L26" s="21"/>
     </row>
     <row r="27" spans="1:12" ht="24.95" customHeight="1" thickTop="1">
-      <c r="A27" s="62" t="s">
+      <c r="A27" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="63"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="63"/>
-      <c r="K27" s="63"/>
-      <c r="L27" s="64"/>
+      <c r="B27" s="109"/>
+      <c r="C27" s="109"/>
+      <c r="D27" s="109"/>
+      <c r="E27" s="109"/>
+      <c r="F27" s="109"/>
+      <c r="G27" s="109"/>
+      <c r="H27" s="109"/>
+      <c r="I27" s="109"/>
+      <c r="J27" s="109"/>
+      <c r="K27" s="109"/>
+      <c r="L27" s="110"/>
     </row>
     <row r="28" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A28" s="74" t="s">
+      <c r="A28" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="75"/>
-      <c r="C28" s="72" t="s">
+      <c r="B28" s="83"/>
+      <c r="C28" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="76"/>
-      <c r="E28" s="77" t="s">
+      <c r="D28" s="84"/>
+      <c r="E28" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="75"/>
-      <c r="G28" s="72" t="s">
+      <c r="F28" s="83"/>
+      <c r="G28" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="H28" s="76"/>
-      <c r="I28" s="77" t="s">
+      <c r="H28" s="84"/>
+      <c r="I28" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="J28" s="75"/>
-      <c r="K28" s="72" t="s">
+      <c r="J28" s="83"/>
+      <c r="K28" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="L28" s="73"/>
+      <c r="L28" s="81"/>
     </row>
     <row r="29" spans="1:12" ht="24.95" customHeight="1" thickTop="1">
-      <c r="A29" s="41" t="str">
+      <c r="A29" s="94" t="str">
         <f>'Ref.'!A1&amp;"  "&amp;'Ref.'!B1&amp;"  "&amp;'Ref.'!C1</f>
         <v xml:space="preserve">
 &lt; 이용 약관&gt;
@@ -2303,216 +2279,264 @@
 제8조. (분쟁해결 및 관할법원) 본 약관에 대한 분쟁이 발생할 경우 "갑"과 "을"은 양 당사자의 합의에 의해 해결하기로 하며, 합의가 이루어지지 않을 경우 서울중앙지방법원을 관할법원으로 한다.
 </v>
       </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="43"/>
+      <c r="B29" s="95"/>
+      <c r="C29" s="95"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="95"/>
+      <c r="H29" s="95"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="96"/>
     </row>
     <row r="30" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A30" s="44"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="46"/>
+      <c r="A30" s="97"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="98"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="98"/>
+      <c r="H30" s="98"/>
+      <c r="I30" s="98"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="98"/>
+      <c r="L30" s="99"/>
     </row>
     <row r="31" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A31" s="44"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="46"/>
+      <c r="A31" s="97"/>
+      <c r="B31" s="98"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
+      <c r="L31" s="99"/>
     </row>
     <row r="32" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A32" s="44"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="46"/>
+      <c r="A32" s="97"/>
+      <c r="B32" s="98"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="98"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="99"/>
     </row>
     <row r="33" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A33" s="44"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="46"/>
+      <c r="A33" s="97"/>
+      <c r="B33" s="98"/>
+      <c r="C33" s="98"/>
+      <c r="D33" s="98"/>
+      <c r="E33" s="98"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="98"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="98"/>
+      <c r="J33" s="98"/>
+      <c r="K33" s="98"/>
+      <c r="L33" s="99"/>
     </row>
     <row r="34" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A34" s="44"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="46"/>
+      <c r="A34" s="97"/>
+      <c r="B34" s="98"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98"/>
+      <c r="H34" s="98"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98"/>
+      <c r="K34" s="98"/>
+      <c r="L34" s="99"/>
     </row>
     <row r="35" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A35" s="44"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="45"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="46"/>
+      <c r="A35" s="97"/>
+      <c r="B35" s="98"/>
+      <c r="C35" s="98"/>
+      <c r="D35" s="98"/>
+      <c r="E35" s="98"/>
+      <c r="F35" s="98"/>
+      <c r="G35" s="98"/>
+      <c r="H35" s="98"/>
+      <c r="I35" s="98"/>
+      <c r="J35" s="98"/>
+      <c r="K35" s="98"/>
+      <c r="L35" s="99"/>
     </row>
     <row r="36" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A36" s="44"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="45"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="46"/>
+      <c r="A36" s="97"/>
+      <c r="B36" s="98"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="98"/>
+      <c r="E36" s="98"/>
+      <c r="F36" s="98"/>
+      <c r="G36" s="98"/>
+      <c r="H36" s="98"/>
+      <c r="I36" s="98"/>
+      <c r="J36" s="98"/>
+      <c r="K36" s="98"/>
+      <c r="L36" s="99"/>
     </row>
     <row r="37" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A37" s="44"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="45"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="46"/>
+      <c r="A37" s="97"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="98"/>
+      <c r="E37" s="98"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="98"/>
+      <c r="H37" s="98"/>
+      <c r="I37" s="98"/>
+      <c r="J37" s="98"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="99"/>
     </row>
     <row r="38" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A38" s="44"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="45"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="46"/>
+      <c r="A38" s="97"/>
+      <c r="B38" s="98"/>
+      <c r="C38" s="98"/>
+      <c r="D38" s="98"/>
+      <c r="E38" s="98"/>
+      <c r="F38" s="98"/>
+      <c r="G38" s="98"/>
+      <c r="H38" s="98"/>
+      <c r="I38" s="98"/>
+      <c r="J38" s="98"/>
+      <c r="K38" s="98"/>
+      <c r="L38" s="99"/>
     </row>
     <row r="39" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A39" s="44"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="45"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="46"/>
+      <c r="A39" s="97"/>
+      <c r="B39" s="98"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="98"/>
+      <c r="E39" s="98"/>
+      <c r="F39" s="98"/>
+      <c r="G39" s="98"/>
+      <c r="H39" s="98"/>
+      <c r="I39" s="98"/>
+      <c r="J39" s="98"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="99"/>
     </row>
     <row r="40" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A40" s="44"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="45"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="46"/>
+      <c r="A40" s="97"/>
+      <c r="B40" s="98"/>
+      <c r="C40" s="98"/>
+      <c r="D40" s="98"/>
+      <c r="E40" s="98"/>
+      <c r="F40" s="98"/>
+      <c r="G40" s="98"/>
+      <c r="H40" s="98"/>
+      <c r="I40" s="98"/>
+      <c r="J40" s="98"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="99"/>
     </row>
     <row r="41" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A41" s="44"/>
-      <c r="B41" s="45"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="45"/>
-      <c r="G41" s="45"/>
-      <c r="H41" s="45"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="45"/>
-      <c r="K41" s="45"/>
-      <c r="L41" s="46"/>
+      <c r="A41" s="97"/>
+      <c r="B41" s="98"/>
+      <c r="C41" s="98"/>
+      <c r="D41" s="98"/>
+      <c r="E41" s="98"/>
+      <c r="F41" s="98"/>
+      <c r="G41" s="98"/>
+      <c r="H41" s="98"/>
+      <c r="I41" s="98"/>
+      <c r="J41" s="98"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="99"/>
     </row>
     <row r="42" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A42" s="44"/>
-      <c r="B42" s="45"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="45"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="45"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="46"/>
+      <c r="A42" s="97"/>
+      <c r="B42" s="98"/>
+      <c r="C42" s="98"/>
+      <c r="D42" s="98"/>
+      <c r="E42" s="98"/>
+      <c r="F42" s="98"/>
+      <c r="G42" s="98"/>
+      <c r="H42" s="98"/>
+      <c r="I42" s="98"/>
+      <c r="J42" s="98"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="99"/>
     </row>
     <row r="43" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A43" s="47"/>
-      <c r="B43" s="48"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
-      <c r="L43" s="49"/>
+      <c r="A43" s="100"/>
+      <c r="B43" s="101"/>
+      <c r="C43" s="101"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="101"/>
+      <c r="F43" s="101"/>
+      <c r="G43" s="101"/>
+      <c r="H43" s="101"/>
+      <c r="I43" s="101"/>
+      <c r="J43" s="101"/>
+      <c r="K43" s="101"/>
+      <c r="L43" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="A29:L43"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C12:L12"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="K19:L19"/>
@@ -2529,54 +2553,6 @@
     <mergeCell ref="I11:L11"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C12:L12"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C14:L14"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="A29:L43"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="A27:L27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A13:B13">
@@ -2633,57 +2609,33 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="32" t="s">
-        <v>50</v>
-      </c>
+      <c r="A2" s="25"/>
+      <c r="B2" s="32"/>
       <c r="C2" s="26"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>51</v>
-      </c>
+      <c r="A3" s="25"/>
+      <c r="B3" s="32"/>
       <c r="C3" s="26"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>52</v>
-      </c>
+      <c r="A4" s="25"/>
+      <c r="B4" s="32"/>
       <c r="C4" s="26"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>53</v>
-      </c>
+      <c r="A5" s="25"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="26"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>54</v>
-      </c>
+      <c r="A6" s="25"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="26"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>54</v>
-      </c>
+      <c r="A7" s="25"/>
+      <c r="B7" s="32"/>
       <c r="C7" s="26"/>
     </row>
     <row r="8" spans="1:3">
